--- a/content/thoughts.xlsx
+++ b/content/thoughts.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N605"/>
+  <dimension ref="A1:N636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -38946,6 +38946,2078 @@
         </is>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>605</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>It may be answered that one should wish to be both, but, because it is difficult to unite them in one person, it is much safer to be feared than loved, when, of the two, either must be dispensed with.</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Niccolò Machiavelli, The Prince, ch. 17</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Machiavelli (1469–1527), a Florentine diplomat, wrote The Prince after losing his post. His reasoning: people are fickle, so love can break, while fear holds. He adds that a ruler must never be hated.</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>W. K. Marriott (1908) | https://www.gutenberg.org/ebooks/1232</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Would you rather be feared or loved, and what would each cost you?</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>Character and virtue</t>
+        </is>
+      </c>
+      <c r="K606" t="n">
+        <v>2</v>
+      </c>
+      <c r="L606" t="n">
+        <v>5</v>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>Author intro is here; move it if another Machiavelli thought comes first in the calendar.</t>
+        </is>
+      </c>
+      <c r="N606" s="2" t="inlineStr">
+        <is>
+          <t>Chapter 17 of The Prince asks whether it is better for a ruler to be loved or feared. Machiavelli wrote the book in 1513, the year after the Medici returned to Florence and dismissed him from the post he had held since 1494. His answer rests on a bleak view of people: “as long as you succeed they are yours entirely”, but when danger comes close they turn against you.
+Love, he argues, is a bond of obligation that people break whenever it suits them, while fear holds because the dread of punishment never fails. Yet he sets a limit: a ruler must avoid being hated. Few of us rule anyone, but the choice is familiar. Do we rely on goodwill, or only on what we can enforce?</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>606</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>…men judge generally more by the eye than by the hand, because it belongs to everybody to see you, to few to come in touch with you. Every one sees what you appear to be, few really know what you are …</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Niccolò Machiavelli, The Prince, ch. 18</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Most people only see how you appear; few get close enough to know who you are. Machiavelli meant it as advice to rulers. Today it also reads as a warning about living for appearances.</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>W. K. Marriott (1908) | https://www.gutenberg.org/ebooks/1232</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Who knows who you really are, and not just how you appear?</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Self-knowledge</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>Ego, pride, and humility</t>
+        </is>
+      </c>
+      <c r="K607" t="n">
+        <v>2</v>
+      </c>
+      <c r="L607" t="n">
+        <v>5</v>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>Kept "men" (English source, word for word). The same paragraph calls appearing religious the most useful quality; not quoted.</t>
+        </is>
+      </c>
+      <c r="N607" s="2" t="inlineStr">
+        <is>
+          <t>In chapter 18, Machiavelli lists the qualities a prince should seem to have, such as mercy, good faith and honesty. Seeming, he insists, matters more than being, because people judge by what they see. Only a few get close enough to know the truth, and “those few dare not oppose themselves to the opinion of the many”.
+It is cold advice, written for rulers who need to keep power. Yet it describes something everyone knows. Most people meet only our surface: a face, a role, a reputation. Read the other way round, the line is also an invitation. It asks who the few are who really know us, and whether we let anyone come close enough to touch, and not just to see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>607</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>…in the beginning of the malady it is easy to cure but difficult to detect, but in the course of time, not having been either detected or treated in the beginning, it becomes easy to detect but difficult to cure.</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Niccolò Machiavelli, The Prince, ch. 3</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Machiavelli borrows a saying from doctors: early on, an illness is easy to cure but hard to spot; later it is easy to spot but hard to cure. He meant trouble in a state. It fits habits and relationships too.</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>W. K. Marriott (1908) | https://www.gutenberg.org/ebooks/1232</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Which small problem are you noticing now that will be harder to fix later?</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Habit and practice</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>Work and action</t>
+        </is>
+      </c>
+      <c r="K608" t="n">
+        <v>2</v>
+      </c>
+      <c r="L608" t="n">
+        <v>4</v>
+      </c>
+      <c r="N608" s="2" t="inlineStr">
+        <is>
+          <t>Chapter 3 of The Prince explains how the Romans held new lands. They dealt with future troubles early, and Machiavelli praises them for it. To make the point, he borrows what doctors said of “hectic fever”. Then he applies it to the state: troubles foreseen early “can be quickly redressed”, but once everyone can see them, “there is no longer a remedy”.
+The pattern is everywhere. A small resentment between friends, an unpaid bill, a habit that is starting to take hold: each is easy to fix while it is still hard to notice. By the time it is obvious, it costs far more. The lesson is attention. Looking closely at small things, before they demand it, is often the cheapest care we can give.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>608</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>…there is nothing more difficult to take in hand, more perilous to conduct, or more uncertain in its success, than to take the lead in the introduction of a new order of things, because the innovator has for enemies all those who have done well under the old conditions, and lukewarm defenders in those who may do well under the new.</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Niccolò Machiavelli, The Prince, ch. 6</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Change is hard to lead because the people it will hurt know it now, while those it will help cannot yet be sure. Five centuries later, anyone who has led change at work will recognise this.</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>W. K. Marriott (1908) | https://www.gutenberg.org/ebooks/1232</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>If your idea succeeds, who loses, and how will they react?</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Change and impermanence</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="K609" t="n">
+        <v>3</v>
+      </c>
+      <c r="L609" t="n">
+        <v>5</v>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>Full stop added at the end (the source sentence continues after a full stop in Marriott's text; check).</t>
+        </is>
+      </c>
+      <c r="N609" s="2" t="inlineStr">
+        <is>
+          <t>Chapter 6 of The Prince is about rulers who rise by their own ability, like Cyrus, Romulus and Theseus. They win power with difficulty, Machiavelli says, partly because they must bring in new rules and methods. Supporters stay cool, partly from fear of opponents and partly because people “do not readily believe in new things until they have had a long experience of them”.
+The imbalance is the heart of it. Those who stand to lose know exactly what they will lose, and fight hard. Those who stand to gain cannot see it yet, so they help only half-heartedly. Anyone who has tried to change a workplace or a family habit will know the feeling. It helps to expect it, and to give new ways time to prove themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>609</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>…envy is ever joined with the comparing of a man's self; and where there is no comparison, no envy …</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Francis Bacon, Essays, 'Of Envy'</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Francis Bacon (1561–1626), English statesman and philosopher, wrote short essays of practical wisdom. Envy needs a comparison: we only envy those we measure ourselves against. "A man's self" simply means oneself.</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Original English (1625), lightly modernised | https://www.gutenberg.org/ebooks/575</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Who do you compare yourself with, and does it help you?</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Ego, pride, and humility</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>Mind and emotions</t>
+        </is>
+      </c>
+      <c r="K610" t="n">
+        <v>1</v>
+      </c>
+      <c r="L610" t="n">
+        <v>5</v>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>Kept "a man's self" (English source, word for word); the About explains it. Author intro is here.</t>
+        </is>
+      </c>
+      <c r="N610" s="2" t="inlineStr">
+        <is>
+          <t>Bacon's essay 'Of Envy' sorts people into those most apt to envy and those most likely to be envied. Relatives, colleagues and those raised together, he notes, envy one another most when one of them rises. People of real merit who are promoted are envied less, because their good fortune seems no more than their due: “no man envieth the payment of a debt”.
+This line explains why. Envy needs a comparison, and we compare ourselves with those close to us. As Bacon goes on, “kings are not envied, but by kings”. We rarely envy a stranger's fame, yet a friend's success can sting. Knowing this helps. When envy appears, it shows who we are measuring ourselves against, and invites us to ask whether that measure is a fair one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>610</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Reading makes a full man; conference a ready man; and writing an exact man.</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Francis Bacon, Essays, 'Of Studies'</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Reading fills the mind, conversation makes it quick, and writing makes it precise. In Bacon's English, "conference" meant conversation and "exact" meant precise. Each gives something the others cannot.</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Original English (1625), lightly modernised | https://www.gutenberg.org/ebooks/575</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Which do you do least: reading, talking, or writing?</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Learning and knowledge</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>Habit and practice</t>
+        </is>
+      </c>
+      <c r="K611" t="n">
+        <v>2</v>
+      </c>
+      <c r="L611" t="n">
+        <v>5</v>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>"maketh" modernised to "makes" (light modernisation, credited).</t>
+        </is>
+      </c>
+      <c r="N611" s="2" t="inlineStr">
+        <is>
+          <t>Bacon's essay 'Of Studies' is about what learning does for us, and how to use it. It holds his famous advice that “Some books are to be tasted, others to be swallowed, and some few to be chewed and digested”. Right after this line, he spells out the trade-offs: whoever writes little needs a great memory, and whoever talks little with others needs a quick wit.
+Each habit trains a different part of the mind. Reading fills it with material. Conversation makes us ready to think on our feet, because others push back. Writing forces precision, since vague ideas fall apart on the page. Bacon also warns against reading only to contradict, or only to believe. We should read, he says, “to weigh and consider”. The three habits work best together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>611</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>"I also know," said Candide, "that we must cultivate our garden."</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Voltaire, Candide, ch. 30</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Near the end of Candide (1759), Voltaire's comic novel. Through war, shipwreck, and earthquake, Candide's teacher insists all is for the best. Settled at last on a small farm, Candide stops arguing: tend to what is within reach, and work at it.</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/4650</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>What is your garden: the small thing within reach that deserves your care?</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Work and action</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>Purpose and meaning</t>
+        </is>
+      </c>
+      <c r="K612" t="n">
+        <v>1</v>
+      </c>
+      <c r="L612" t="n">
+        <v>5</v>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Je sais aussi, dit Candide, qu’il faut cultiver notre jardin. » About is 44 words, a little above the usual length, as you asked for solid context. The teacher's reply mentions the Garden of Eden; not quoted.</t>
+        </is>
+      </c>
+      <c r="N612" s="2" t="inlineStr">
+        <is>
+          <t>Candide is Voltaire's comic attack on easy optimism. Its young hero is taught by his tutor Pangloss that all is for the best, then lives through war, shipwreck, an earthquake and worse. In the last chapter, the friends meet an old farmer near Constantinople who works his twenty acres with his children. Work, the old man says, keeps away three great evils: boredom, vice and need.
+When Pangloss starts listing kings who came to bad ends, Candide cuts him short with this line. Instead of arguing about the best of all possible worlds, the little group gets to work. The book ends with Candide saying it once more, in reply to Pangloss. The garden can be read in many ways: a plot of land, a job, a mind. Whatever it is, it needs tending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>612</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Friendship is the marriage of the soul, and this marriage is open to divorce.</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Voltaire, Philosophical Dictionary, 'Friendship'</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Voltaire (1694–1778), the great wit of the French Enlightenment, wrote this in his Philosophical Dictionary. Friendship is freely chosen, so it can also end, which is part of what makes it precious.</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/Dictionnaire_philosophique/Garnier_(1878)</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Which friendship needs some care before it quietly fades?</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Friendship and kindness</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="K613" t="n">
+        <v>1</v>
+      </c>
+      <c r="L613" t="n">
+        <v>5</v>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « L’amitié est le mariage de l’âme, et ce mariage est sujet au divorce. » Author intro is here.</t>
+        </is>
+      </c>
+      <c r="N613" s="2" t="inlineStr">
+        <is>
+          <t>Voltaire's article on friendship appeared in his Philosophical Dictionary in 1764, and this line was then its opening. The joke that now comes first was added in 1770: people have long spoken of the temple of Friendship, and everyone knows it has had few visitors. Friendship, he adds, cannot be ordered, any more than love or esteem.
+Right after this line, he calls friendship an unspoken contract between two people who are sensitive and good. The wicked have only accomplices, he says, pleasure-seekers have companions, the self-interested have partners; only the virtuous have friends. Because friendship is freely chosen, it can also end. That is not a flaw. It means that every day a friendship lasts, both people are choosing it again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>613</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>What is tolerance? It is the mark of our humanity. We are all made of weakness and error; let us forgive one another our foolishness: that is the first law of nature.</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Voltaire, Philosophical Dictionary, 'Tolerance'</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Voltaire spent years campaigning against persecution. His answer here is simple: since everyone is weak and makes mistakes, forgiving one another is the most natural rule there is.</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/Dictionnaire_philosophique/Garnier_(1878)</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Whose foolishness could you forgive today, remembering your own?</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Friendship and kindness</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>Character and virtue</t>
+        </is>
+      </c>
+      <c r="K614" t="n">
+        <v>1</v>
+      </c>
+      <c r="L614" t="n">
+        <v>5</v>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Qu’est-ce que la tolérance ? C’est l’apanage de l’humanité. Nous sommes tous pétris de faiblesses et d’erreurs ; pardonnons-nous réciproquement nos sottises, c’est la première loi de la nature. » "apanage" (an inherited privilege) rendered as "the mark of our humanity"; alternative: "humanity's birthright". The article is about religious quarrels; this passage is not.</t>
+        </is>
+      </c>
+      <c r="N614" s="2" t="inlineStr">
+        <is>
+          <t>This line opens the second section of Voltaire's article on tolerance in the Philosophical Dictionary. The first section ends by recalling how long blood flowed across Europe over arguments of doctrine, until tolerance alone could stop it. Right after this line, he pictures the exchanges of Amsterdam and London, where traders of many faiths do business side by side in peace.
+His argument is short. We are all made of weakness and error, so none of us is in a position to punish others for theirs. Forgiving one another's foolishness is not a generous extra; it is the first law of nature, the rule that follows from what we are. It applies at work and at home too, where it is easy to count other people's mistakes and forget our own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>614</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Prejudice is an opinion without judgement. All over the world, children are taught whatever opinions people like, before they are able to judge.</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Voltaire, Philosophical Dictionary, 'Prejudice'</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>In French the wordplay is plain: préjugé means "pre-judged". A prejudice is a verdict reached before any judging, often handed to us as children, before we could think for ourselves.</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/Dictionnaire_philosophique/Garnier_(1878)</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Which opinion did you receive as a child and never examine?</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Learning and knowledge</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>Freedom, choice, and intention</t>
+        </is>
+      </c>
+      <c r="K615" t="n">
+        <v>1</v>
+      </c>
+      <c r="L615" t="n">
+        <v>5</v>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Le préjugé est une opinion sans jugement. Ainsi dans toute la terre on inspire aux enfants toutes les opinions qu’on veut, avant qu’ils puissent juger. » Wordplay explained in the About rather than forced into the quote. Close in spirit to du Châtelet #196; keep them apart in the calendar.</t>
+        </is>
+      </c>
+      <c r="N615" s="2" t="inlineStr">
+        <is>
+          <t>In the Philosophical Dictionary, Voltaire's short article on prejudice opens with this definition, then makes a surprising turn: some prejudices are good. Everywhere, he notes, children are taught to love their parents and to see theft as a crime before they can know what a vice or a virtue is. Good prejudices are the ones our judgement confirms once we reason.
+The trouble is the rest. He imagines a child taught to bow before a man in certain clothes who walks and speaks gravely. Grown up, the child sees a charlatan full of pride, and the prejudice gives way to judgement. Much of what we believe reached us before we could check it. The task is not to throw it all out, but to test it and keep what holds up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>615</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>It is better to risk saving a guilty person than to condemn an innocent one.</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Voltaire, Zadig, ch. 6</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>From Zadig (1747), one of Voltaire's tales. Punishing an innocent person is worse than letting a guilty one go free. The English judge William Blackstone made the same point in 1769.</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/4647</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>When have you judged someone before you knew the whole story?</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>Character and virtue</t>
+        </is>
+      </c>
+      <c r="K616" t="n">
+        <v>1</v>
+      </c>
+      <c r="L616" t="n">
+        <v>5</v>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Qu'il vaut mieux hasarder de sauver un coupable que de condamner un innocent. » Degendered ("un coupable" = a guilty man).</t>
+        </is>
+      </c>
+      <c r="N616" s="2" t="inlineStr">
+        <is>
+          <t>In chapter 6 of Zadig, the young hero becomes first minister of Babylon. Voltaire paints him as a model judge: when he judged a case, it was not he who judged but the law, and when the law was too severe, he softened it. Nations owe this great principle to Zadig, Voltaire says with a wink.
+The idea is simple: punishing an innocent person is a deeper wrong than letting a guilty one go. It asks something hard of us, which is to accept that some guilty people will go free. It also reaches beyond the courtroom. Before we condemn someone on thin evidence, at work or among friends, it is worth asking which mistake we would rather make.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>616</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Such is the human condition that to wish for your country's greatness is to wish harm on your neighbours. Whoever wanted their homeland never to be bigger or smaller, richer or poorer, would be a citizen of the universe.</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Voltaire, Philosophical Dictionary, 'Homeland'</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Voltaire points to an uncomfortable truth: wanting your country to be great often means wanting others to lose. His alternative is the old ideal of the citizen of the world, loyal to people everywhere.</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/Dictionnaire_philosophique/Garnier_(1878)</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Where does loyalty to your own group cost someone else?</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>Friendship and kindness</t>
+        </is>
+      </c>
+      <c r="K617" t="n">
+        <v>3</v>
+      </c>
+      <c r="L617" t="n">
+        <v>5</v>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Telle est donc la condition humaine, que souhaiter la grandeur de son pays c’est souhaiter du mal à ses voisins. Celui qui voudrait que sa patrie ne fût jamais ni plus grande, ni plus petite, ni plus riche, ni plus pauvre, serait le citoyen de l’univers. »</t>
+        </is>
+      </c>
+      <c r="N617" s="2" t="inlineStr">
+        <is>
+          <t>The Philosophical Dictionary's article on the homeland ranges widely, from the first republics to forms of government. Near the end it turns darker. It is sad, he writes, that being a good patriot so often means being the enemy of the rest of humanity. He recalls Cato the Elder, who always added, when giving his view in the Roman senate, that Carthage should be destroyed.
+His reasoning is plain. A good patriot wants their city rich through trade and strong in arms, but one country cannot gain without another losing. His way out is not to stop caring, but to care for everyone alike. It is a demanding ideal. It asks whether loyalty to our own can live alongside goodwill to all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>617</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>As soon as anyone says of public affairs, "What does it matter to me?", the state should be counted as lost.</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Rousseau, The Social Contract, Book III, ch. 15</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Rousseau (1712–1778), born in Geneva, believed freedom depends on citizens taking part. Once people stop caring about shared affairs, others start deciding for them.</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/Du_contrat_social/%C3%89dition_1762</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Which shared matter have you left for others to decide?</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>Freedom, choice, and intention</t>
+        </is>
+      </c>
+      <c r="K618" t="n">
+        <v>1</v>
+      </c>
+      <c r="L618" t="n">
+        <v>5</v>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Sitôt que quelqu’un dit des affaires de l’État, que m’importe ? on doit compter que l’État est perdu. » Author intro is here.</t>
+        </is>
+      </c>
+      <c r="N618" s="2" t="inlineStr">
+        <is>
+          <t>Book III, chapter 15 of The Social Contract deals with deputies, the representatives of the people, and Rousseau distrusts them. In a well-run city, he writes, everyone hurries to the assemblies. Under bad government no one will take a step to attend, because no one expects the common will to win and private cares absorb everything. He also warns against paying others to do our civic duties: give money, and soon you will have chains.
+This line marks the turning point. Once citizens shrug at public affairs, others begin deciding for them, and freedom slips away quietly. The warning holds for any shared life, from a nation to a neighbourhood or a family. What nobody cares for falls to whoever is still paying attention, and their interests may not be ours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>618</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>The person who has lived the most is not the one who has counted the most years, but the one who has most felt life.</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Rousseau, Emile, Book I</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>From Emile (1762), Rousseau's book on education. A long life and a full one are not the same; what counts is how deeply we feel the life we have. Montaigne made a similar point two centuries earlier.</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/%C3%89mile,_ou_De_l%E2%80%99%C3%A9ducation/%C3%89dition_1782</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>When did you last feel fully alive?</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Purpose and meaning</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>Time and the present</t>
+        </is>
+      </c>
+      <c r="K619" t="n">
+        <v>1</v>
+      </c>
+      <c r="L619" t="n">
+        <v>5</v>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « L’homme qui a le plus vécu n’est pas celui qui a compté le plus d’années ; mais celui qui a le plus senti la vie. » Last sentence only, as agreed. Degendered ("L'homme"). Close to Montaigne #278; keep them apart in the calendar.</t>
+        </is>
+      </c>
+      <c r="N619" s="2" t="inlineStr">
+        <is>
+          <t>Book I of Emile, Rousseau's long work on education, criticises parents who raise children as if they would never leave their rooms. He wants children taught to bear the blows of fortune, even in the ice of Iceland or on the burning rock of Malta. The point, he says, is less to stop a child from dying than to make them live.
+Living, he writes just before this line, is not breathing but acting: using our senses, our faculties and every part of ourselves that gives us the feeling of existing. Just after it comes a sharp image: someone buried at a hundred may have died at birth. A life is measured less in years than in how fully we are present in it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>619</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Everything changes around us. We ourselves change, and no one can be sure they will love tomorrow what they love today.</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Rousseau, Reveries of the Solitary Walker, Ninth Walk</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Written in Rousseau's last years, during long walks alone. Even our tastes and loves change, so a happiness that depends on things staying the same cannot last.</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/65434</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>What do you love today that you did not love five years ago?</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Change and impermanence</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="K620" t="n">
+        <v>1</v>
+      </c>
+      <c r="L620" t="n">
+        <v>5</v>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Tout change autour de nous: nous changeons nous-mêmes, et nul ne peut s'assurer qu'il aimera demain ce qu'il aime aujourd'hui; »</t>
+        </is>
+      </c>
+      <c r="N620" s="2" t="inlineStr">
+        <is>
+          <t>The Reveries of the Solitary Walker was Rousseau's last work: ten walks, the tenth written less than three months before his death and left unfinished. The Ninth Walk opens with this reflection, which follows a bleak premise: happiness is a lasting state that does not seem made for us here, since everything on earth is in constant flux.
+From this he draws a gentle lesson. Our plans for lasting happiness are fantasies, so we should enjoy contentment when it comes, take care not to drive it away, and not try to chain it down. Knowing that what we love may change does not make it worth less. It makes today worth noticing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>620</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>I have never believed that human freedom lies in doing what we want, but rather in never doing what we do not want.</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Rousseau, Reveries of the Solitary Walker, Sixth Walk</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Rousseau's idea of freedom is a quiet one: not getting everything we want, but never being made to do what we don't want.</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/65434</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>What are you doing right now that you do not really want to do?</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Freedom, choice, and intention</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>Self-knowledge</t>
+        </is>
+      </c>
+      <c r="K621" t="n">
+        <v>1</v>
+      </c>
+      <c r="L621" t="n">
+        <v>5</v>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Je n'ai jamais cru que la liberté de l'homme consistât à faire ce qu'il veut, mais bien à ne jamais faire ce qu'il ne veut pas, » Degendered ("la liberté de l'homme").</t>
+        </is>
+      </c>
+      <c r="N621" s="2" t="inlineStr">
+        <is>
+          <t>In the Sixth Walk of the Reveries, Rousseau asks why he never fitted into society, where everything is constraint, obligation and duty. When he acts freely, he says, he is good; as soon as he feels the yoke of necessity or of other people, he turns stubborn. His strength is all negative: his faults are faults of leaving things undone, rarely of doing harm.
+This line is his definition of freedom. It is not the power to do whatever we like, but never being made to do what we do not want. He contrasts it with ambitious people, who spend their lives doing what they dislike so that they can command others. How much of what we do each day goes against our own will?</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>621</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>People are born free, and everywhere they are in chains. Some think they are the masters of others, yet are more enslaved than those others.</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Rousseau, The Social Contract, Book I, ch. 1</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>The famous opening of The Social Contract (1762), usually quoted as "Man is born free". Rousseau asks what could make power over others fair, and notes that those who rule are bound too.</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/Du_contrat_social/%C3%89dition_1762</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Which chains do you carry that you have stopped noticing?</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Freedom, choice, and intention</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="K622" t="n">
+        <v>2</v>
+      </c>
+      <c r="L622" t="n">
+        <v>5</v>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « L’homme est né libre, &amp; par-tout il est dans les fers. Tel se croit le maître des autres, qui ne laisse pas d’être plus esclave qu’eux. » Degendered, as you asked. The About mentions the famous wording so readers still recognise it.</t>
+        </is>
+      </c>
+      <c r="N622" s="2" t="inlineStr">
+        <is>
+          <t>The Social Contract opens Book I with these lines. Just before, Rousseau explains why he writes about politics: born a citizen of a free state, he says, his right to vote, however small its weight, obliges him to study public affairs. He admits next that he does not know how this change came about; what he can answer is what could make it legitimate.
+His answer, built up across the book, is that rightful power rests on agreements, not on force. Force alone gives no right, he argues: a people forced to obey does well to obey, but does better still to shake off the yoke when it can. The second sentence adds the sting. Those who think they rule others are bound as well, and often more tightly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>622</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>…you are lost if you forget that the fruits belong to all, and the earth to no one!</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Rousseau, Discourse on Inequality, Part Two</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>From the Discourse on Inequality (1755). Rousseau imagines the first person who fenced off land and said "This is mine", and someone who should have pulled up the stakes and cried this out.</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/Discours_sur_l%E2%80%99origine_et_les_fondements_de_l%E2%80%99in%C3%A9galit%C3%A9_parmi_les_hommes</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>What do you treat as yours that might belong to everyone?</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>Nature and the universe</t>
+        </is>
+      </c>
+      <c r="K623" t="n">
+        <v>3</v>
+      </c>
+      <c r="L623" t="n">
+        <v>5</v>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « vous êtes perdus, si vous oubliez que les fruits sont à tous, et que la terre n’est à personne ! » Last part only, as you suggested.</t>
+        </is>
+      </c>
+      <c r="N623" s="2" t="inlineStr">
+        <is>
+          <t>The second part of Rousseau's Discourse on Inequality opens with a famous scene. The first person who fenced off a piece of land, thought of saying 'This is mine', and found people simple enough to believe it, was the true founder of civil society. Rousseau then imagines someone pulling up the stakes or filling in the ditch, and warning everyone not to listen to this impostor.
+How many crimes, wars and miseries, he asks, that person would have spared humanity. This line is the cry itself. Rousseau admits that the idea of property grew slowly, and that by then things could probably not have stayed as they were. Still, the cry asks us to remember what is shared: the earth was here before any of us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>623</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Leisure is the mother of Philosophy; and Common-wealth, the mother of Peace, and Leisure.</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Thomas Hobbes, Leviathan, ch. 46</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Thomas Hobbes (1588–1679) lived through England's civil wars. By "common-wealth" he means an organised state, not today's Commonwealth of Nations. Only where a state keeps the peace do people have time to think.</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Original English (1651), lightly modernised | https://www.gutenberg.org/ebooks/3207</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>What gives you the calm and free time to think, and who helps make it possible?</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Learning and knowledge</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="K624" t="n">
+        <v>2</v>
+      </c>
+      <c r="L624" t="n">
+        <v>4</v>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>"Leasure" modernised to "Leisure"; final colon changed to a full stop (light modernisation, credited). Author intro is here.</t>
+        </is>
+      </c>
+      <c r="N624" s="2" t="inlineStr">
+        <is>
+          <t>Chapter 46 of Leviathan is an attack on what Hobbes calls vain philosophy, and here he looks back at how philosophy began. True and useful ideas existed from the start, he says, like corn and vines growing wild before anyone planted them. But people lacked the time to cultivate them, busy with the necessities of life and with defending themselves against their neighbours.
+Only great states changed that. “Where first were great and flourishing Cities, there was first the study of Philosophy”, Hobbes writes. Thinking needs safety. People struggling to survive, or living in fear, have no time to wonder about anything else. Peace and free time are not luxuries for thought but its ground. It is worth remembering on busy days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>624</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>…new opinions are always suspected, and usually opposed, without any other reason but because they are not already common. But truth, like gold, is not the less so for being newly brought out of the mine.</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>John Locke, An Essay Concerning Human Understanding, Epistle Dedicatory</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>John Locke (1632–1704), English philosopher, wrote this while presenting his own new ideas. New thinking is often rejected only because it is new, but a truth is no less true for being recently found.</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Original English (1690) | https://www.gutenberg.org/ebooks/10615</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Which idea do you resist mainly because it is unfamiliar?</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Learning and knowledge</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>Change and impermanence</t>
+        </is>
+      </c>
+      <c r="K625" t="n">
+        <v>2</v>
+      </c>
+      <c r="L625" t="n">
+        <v>5</v>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>Starts at "new opinions", as you suggested. Author intro is here.</t>
+        </is>
+      </c>
+      <c r="N625" s="2" t="inlineStr">
+        <is>
+          <t>An Essay Concerning Human Understanding opens with a letter dedicating the book to Thomas, Earl of Pembroke and Montgomery. Locke knows his ideas are new and expects resistance. “The imputation of Novelty is a terrible charge”, he writes, among those who judge “of men’s heads, as they do of their perukes, by the fashion”, that is, like their wigs.
+The image of gold carries the argument. It is “trial and examination” that must give truth its value, he goes on, not any antique fashion. A new idea is not right because it is new, and not wrong either. It has to be tested. When we dismiss an idea, is it because we have weighed it, or only because we have not heard it before?</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>625</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>…the end of law is not to abolish or restrain, but to preserve and enlarge freedom: for in all the states of created beings capable of laws, where there is no law, there is no freedom …</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>John Locke, Second Treatise of Government, ch. 6, sect. 57</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Just before this, Locke says a fence that keeps us from bogs and cliffs hardly deserves to be called a prison. Good laws do not shrink our freedom; they protect it from other people's force.</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Original English (1690) | https://www.gutenberg.org/ebooks/7370</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Which rule in your life gives you more freedom, not less?</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Freedom, choice, and intention</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="K626" t="n">
+        <v>3</v>
+      </c>
+      <c r="L626" t="n">
+        <v>4</v>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>"created beings" may hint at a Creator; if you'd rather avoid it, cut after "enlarge freedom".</t>
+        </is>
+      </c>
+      <c r="N626" s="2" t="inlineStr">
+        <is>
+          <t>Chapter 6 of Locke's Second Treatise of Government is about the power of parents over their children. Children are not born able to reason, Locke argues, so they are not yet fully free, and guidance helps them grow into freedom. Law, he writes, is “not so much the limitation as the direction of a free and intelligent agent to his proper interest”.
+Then comes his image: “that ill deserves the name of confinement which hedges us in only from bogs and precipices”. Freedom, he goes on, is not doing whatever we please, “for who could be free, when every other man’s humour might domineer over him?” It means not living under another person's arbitrary will. The right rules do not shrink our room to act; they protect it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>626</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>There are only three events in a person's life: being born, living, and dying. We do not feel ourselves being born, we suffer in dying, and we forget to live.</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Jean de La Bruyère, The Characters, 'Of Man', 48</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Jean de La Bruyère (1645–1696) wrote The Characters, sharp portraits of people at the French court. Of life's three events, only the middle one is in our hands, and it is the one we forget.</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/17980</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>What would "not forgetting to live" look like for you this week?</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Death and mortality</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>Time and the present</t>
+        </is>
+      </c>
+      <c r="K627" t="n">
+        <v>1</v>
+      </c>
+      <c r="L627" t="n">
+        <v>5</v>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Il n'y a pour l'homme que trois événements: naître, vivre et mourir. Il ne se sent pas naître, il souffre à mourir, et il oublie de vivre. » Degendered ("l'homme"). Author intro is here.</t>
+        </is>
+      </c>
+      <c r="N627" s="2" t="inlineStr">
+        <is>
+          <t>The Characters, first published in 1688, gathers La Bruyère's remarks and portraits of the people of his time, printed with his translation of the Greek writer Theophrastus. This remark sits in the chapter 'Of Man', in a run of thoughts on time and death. Just before it, he compares life to a sleep from which the old only begin to wake when it is time to die.
+His point is sharp and a little sad. Of life's three events, we do not feel the first and we suffer the last, while the middle one, the only one we can do anything with, slips by unnoticed. We spend so much thought on beginnings and endings that we neglect the living in between. The line is a quiet nudge to pay attention to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>627</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Children have no past and no future, and, something we rarely manage, they enjoy the present.</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Jean de La Bruyère, The Characters, 'Of Man', 51</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Children live in the present without trying. Adults spend much of their time in regret or worry, and have to learn again what children have never forgotten.</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/17980</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>When did you last enjoy a moment without thinking of before or after?</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Time and the present</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Happiness and the good life</t>
+        </is>
+      </c>
+      <c r="K628" t="n">
+        <v>1</v>
+      </c>
+      <c r="L628" t="n">
+        <v>5</v>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Les enfants n'ont ni passé ni avenir, et, ce qui ne nous arrive guère, ils jouissent du présent. »</t>
+        </is>
+      </c>
+      <c r="N628" s="2" t="inlineStr">
+        <is>
+          <t>This remark in the chapter 'Of Man' of La Bruyère's Characters comes right after a far less flattering one. There he lists children's faults: they are proud, envious, idle, fickle and quick-tempered, laughing and crying easily over very small things. They are, he concludes, already adults.
+Then comes this gentler observation. Children carry no regrets and fret over no plans, so they can simply enjoy the moment. La Bruyère admits, in passing, that this rarely happens to us. Adults live much of the time somewhere else, going over the past or worrying about what comes next. We cannot become children again. We can, now and then, give the present our whole attention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>628</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>It is a great misfortune to have neither enough wit to speak well nor enough judgement to keep quiet.</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Jean de La Bruyère, The Characters, 'Of Society and Conversation', 18</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Speaking well and knowing when to stay quiet are two different skills. Lacking both, La Bruyère adds, is where all rudeness begins.</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/17980</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>When would silence have served you better than words?</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Self-knowledge</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>Character and virtue</t>
+        </is>
+      </c>
+      <c r="K629" t="n">
+        <v>1</v>
+      </c>
+      <c r="L629" t="n">
+        <v>5</v>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « C'est une grande misère que de n'avoir pas assez d'esprit pour bien parler, ni assez de jugement pour se taire. »</t>
+        </is>
+      </c>
+      <c r="N629" s="2" t="inlineStr">
+        <is>
+          <t>In the chapter 'Of Society and Conversation', La Bruyère sketches the people who spoil talk: those who speak before they think, and those who weigh every word so carefully that listening to them becomes hard work. Just before this remark, he warns that conversation should rest on good sense and judgement rather than on too much imagination.
+Speaking well and keeping quiet are separate gifts, and missing both, he adds, is the source of all tactless talk. Most of us have at least one of them. Some people speak brilliantly but never know when to stop; others say little, but at the right moment. The line invites a little self-knowledge: which gift do we have, and which one could we practise?</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>629</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>The art of conversation lies much less in showing your own wit than in helping others find theirs: whoever leaves a conversation with you pleased with themselves and their own cleverness is perfectly pleased with you.</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Jean de La Bruyère, The Characters, 'Of Society and Conversation', 16</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>People leave a good conversation pleased with themselves, not with you, and that is exactly why they like you. The best talkers help others shine.</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/17980</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>In your last conversation, who did more of the shining?</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Friendship and kindness</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>Ego, pride, and humility</t>
+        </is>
+      </c>
+      <c r="K630" t="n">
+        <v>2</v>
+      </c>
+      <c r="L630" t="n">
+        <v>5</v>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « L'esprit de la conversation consiste bien moins à en montrer beaucoup qu'à en faire trouver aux autres: celui qui sort de votre entretien content de soi et de son esprit, l'est de vous parfaitement. »</t>
+        </is>
+      </c>
+      <c r="N630" s="2" t="inlineStr">
+        <is>
+          <t>This remark from 'Of Society and Conversation' follows La Bruyère's portrait of careful talkers who never risk a word and speak correctly and boringly. In the same remark, he explains why this works: people do not want to admire you, they want to please. They seek less to be taught, or even entertained, than to be appreciated and applauded.
+His conclusion is that the most delicate pleasure is giving pleasure to others. Good conversation is not a stage for our own cleverness. It works best when we ask, listen and leave room for the other person's ideas. The result looks odd but is true: people leave pleased with themselves, and so with us. Generous attention often wins more than brilliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>630</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>The most wasted of all days is the one on which we have not laughed.</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Nicolas Chamfort, Maxims and Thoughts</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Nicolas Chamfort (1741–1794), a playwright and famous wit of the Paris salons, left notes of maxims published after his death. Laughter, for him, is no luxury: a day without it is a day lost.</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/42377</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>What made you laugh today, or who could?</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Happiness and the good life</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>Time and the present</t>
+        </is>
+      </c>
+      <c r="K631" t="n">
+        <v>1</v>
+      </c>
+      <c r="L631" t="n">
+        <v>5</v>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « La plus perdue de toutes les journées est celle où l'on n'a pas ri. » Author intro is here.</t>
+        </is>
+      </c>
+      <c r="N631" s="2" t="inlineStr">
+        <is>
+          <t>Chamfort's Maxims and Thoughts fill part of the first volume of his Complete Works, printed in Paris in 1824. This one sits in the opening chapter of general maxims, which begins by teasing maxims themselves as shortcuts for lazy minds. Nearby, he compares the philosopher who wants to put out his passions to a chemist who wants to put out his fire.
+Just before this maxim, Chamfort, himself the author of a tragedy, notes that tragic theatre gives too much importance to life and death. Laughter is the counterweight. A day with laughter is one in which something absurd or delightful reached us and we let it in. The editor's notice speaks of Chamfort's bitterness, which makes the line more striking: even he counted a day without laughter as lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>631</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Great thoughts come from the heart.</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Vauvenargues, Reflections and Maxims, 127</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Vauvenargues (1715–1747) was a French soldier who died at 31, much admired by Voltaire. In an age that prized cool reason, he argued that our best ideas begin with feeling.</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/R%C3%A9flexions_et_Maximes_(Vauvenargues)</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Which of your best ideas began as a feeling?</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Mind and emotions</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>Learning and knowledge</t>
+        </is>
+      </c>
+      <c r="K632" t="n">
+        <v>1</v>
+      </c>
+      <c r="L632" t="n">
+        <v>5</v>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « Les grandes pensées viennent du cœur. » Author intro is here.</t>
+        </is>
+      </c>
+      <c r="N632" s="2" t="inlineStr">
+        <is>
+          <t>This maxim, number 127 in this edition of Vauvenargues' Reflections and Maxims, sits in a run of thoughts on reason and feeling. A few maxims earlier, he writes that reason deceives us more often than nature, and that reason does not know the interests of the heart. Just after it, he adds that good instinct has no need of reason, but gives it.
+In his notes, the editor explains that by the heart Vauvenargues means feeling and instinct, and calls this the famous maxim that everyone admires and no one disputes. The idea is not that thinking is useless. It is that our deepest ideas begin with something we care about, and that reason follows and shapes them. Great thoughts often start as a feeling taken seriously.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>632</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>The thought of death deceives us, for it makes us forget to live.</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Vauvenargues, Reflections and Maxims, 143</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Thinking about death can be useful, but too much of it steals the life we still have. Spinoza said something similar: the wise think of life, not death.</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/R%C3%A9flexions_et_Maximes_(Vauvenargues)</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Which fear about an ending is taking room from enjoying something now?</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Death and mortality</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>Time and the present</t>
+        </is>
+      </c>
+      <c r="K633" t="n">
+        <v>1</v>
+      </c>
+      <c r="L633" t="n">
+        <v>5</v>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « La pensée de la mort nous trompe, car elle nous fait oublier de vivre. » Links to Spinoza #170.</t>
+        </is>
+      </c>
+      <c r="N633" s="2" t="inlineStr">
+        <is>
+          <t>This is maxim 143 of Vauvenargues' Reflections and Maxims, and it comes right after another about death: to do great things, he writes, we must live as if we were never going to die. The maxim after it is a wry confession. He sometimes tells himself life is too short to be worth worrying about, yet if a bore keeps him from going out, he cannot bear half an hour of it.
+The line warns against a certain kind of gloom. Thinking of death can teach us what matters, but brooding on it draws attention away from the life still in front of us. For Vauvenargues, the remedy is more life, not less.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>633</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Patience is the art of hoping.</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Vauvenargues, Reflections and Maxims, 251</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Patience is not passive waiting. For Vauvenargues it is a skill: keeping hope alive while things take their time.</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/R%C3%A9flexions_et_Maximes_(Vauvenargues)</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>What are you waiting for, and how do you keep your hope alive?</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>Humanists and Essayists</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Suffering and resilience</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>Habit and practice</t>
+        </is>
+      </c>
+      <c r="K634" t="n">
+        <v>1</v>
+      </c>
+      <c r="L634" t="n">
+        <v>5</v>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « La patience est l’art d’espérer. » Patience also appears in Sa'di #574 and #587; keep them apart in the calendar.</t>
+        </is>
+      </c>
+      <c r="N634" s="2" t="inlineStr">
+        <is>
+          <t>Maxim 251 of Vauvenargues' Reflections and Maxims sits among his thoughts on misfortune. Just before it, he notes that necessity eases more sorrows than reason does, and that the favourites of fortune, however unhappy they look to us, never cure us of ambition. Just after it, he adds that despair adds not only to our misery but to our weakness.
+Set beside despair, patience looks different. It is not passive waiting, and it is not giving up. It is hope that has learned to last: the skill of keeping a good outcome in view while time does its work. Despair weakens us; patience keeps our strength for when it is needed. It is a line worth remembering on slow days, when results take longer than we would like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>634</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>…only the passions, and great passions, can raise the soul to great things.</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Denis Diderot, Philosophical Thoughts, I</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Denis Diderot (1713–1784), editor of the great French Encyclopédie, opens his Philosophical Thoughts (1746) by defending the passions. Without strong feeling, he says, there is no great art and no great courage.</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://fr.wikisource.org/wiki/Pens%C3%A9es_philosophiques</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Which passion has pushed you to do something difficult?</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Mind and emotions</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Purpose and meaning</t>
+        </is>
+      </c>
+      <c r="K635" t="n">
+        <v>1</v>
+      </c>
+      <c r="L635" t="n">
+        <v>5</v>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « il n’y a que les passions, et les grandes passions, qui puissent élever l’âme aux grandes choses. » Author intro is here. "Soul" (l'âme) is used in a non-religious sense.</t>
+        </is>
+      </c>
+      <c r="N635" s="2" t="inlineStr">
+        <is>
+          <t>Diderot's Philosophical Thoughts open with this defence of the passions. People rail against them endlessly, he complains, blaming them for all human pain and forgetting that they are also the source of all our pleasures. What annoys him is that they are only ever seen from their bad side, as if a word in their favour were an insult to reason.
+Without the passions, he goes on, nothing is sublime, in conduct or in works; the fine arts return to childhood and virtue becomes petty. The next thought adds that sober passions make ordinary people. Diderot is not praising every impulse. He is saying that strong feeling gives us the energy to love, create and act bravely. Reason can steer, but it needs something to steer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>635</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>I was the absolute master of my old dressing gown; I have become the slave of the new one.</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Denis Diderot, Regrets on My Old Dressing Gown</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Diderot swapped his worn old dressing gown for a beautiful new one. Next to it, his study suddenly looked shabby, so he replaced it piece by piece: a fine desk, a clock, paintings. Today this chain of new wants is called the Diderot effect.</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Translated from the French by The Thinking Place team | https://www.gutenberg.org/ebooks/13863</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Which thing you own has made you want more things?</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Enlightenment Ethics</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Desire and simplicity</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>Freedom, choice, and intention</t>
+        </is>
+      </c>
+      <c r="K636" t="n">
+        <v>1</v>
+      </c>
+      <c r="L636" t="n">
+        <v>5</v>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>Our translation: please check against the French: « J'étais le maître absolu de ma vieille robe de chambre; je suis devenu l'esclave de la nouvelle. » The essay ends with a mock prayer to God; not quoted. This edition dates it 1772 (my research sheet said 1769); the year isn't shown in the app.</t>
+        </is>
+      </c>
+      <c r="N636" s="2" t="inlineStr">
+        <is>
+          <t>Diderot's playful essay Regrets on My Old Dressing Gown carries a subtitle: advice to those who have more taste than fortune. His old gown, he writes, was made for him and he for it. He used it to wipe dusty books and spare ink from his pen, and its long black stains marked a man who works. In the new one, he looks like an idle rich man.
+The new scarlet gown changed everything. Beside it, his straw chair, wooden table and cheap prints looked wrong, so one by one they gave way: a leather armchair, damask hangings, an inlaid cabinet, a mirror, a fine desk, a clock. Today this chain of new wants is often called the Diderot effect, a name given long after him. His line names the cost: what we own can end up owning us.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M605"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content/thoughts.xlsx
+++ b/content/thoughts.xlsx
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>To be happy takes a complete lifetime; for one swallow does not make spring, nor does one fine day; and similarly one day or a brief period of happiness does not make a man supremely blessed and happy.</t>
+          <t>One swallow does not make spring, nor does one fine day; and similarly one day or a brief period of happiness does not make a man supremely blessed and happy.</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">

--- a/content/thoughts.xlsx
+++ b/content/thoughts.xlsx
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Time is like a river made up of the events which happen, and a violent stream; …</t>
+          <t>Time is like a river made up of the events which happen, and a violent stream …</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Love the art, poor as it may be, which you have learned, and be content with it; …</t>
+          <t>Love the art, poor as it may be, which you have learned, and be content with it …</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Constantly regard the universe as one living being, having one substance and one soul; …</t>
+          <t>Constantly regard the universe as one living being, having one substance and one soul …</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>For man, when perfected, is the best of animals, but, when separated from law and justice, he is the worst of all; …</t>
+          <t>For man, when perfected, is the best of animals, but, when separated from law and justice, he is the worst of all …</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Cheerfulness is a direct and immediate gain,—the very coin, as it were, of happiness, …</t>
+          <t>Cheerfulness is a direct and immediate gain,—the very coin, as it were, of happiness …</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>If I can stop one heart from breaking, / I shall not live in vain; …</t>
+          <t>If I can stop one heart from breaking, / I shall not live in vain …</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Much madness is divinest sense / To a discerning eye; …</t>
+          <t>Much madness is divinest sense / To a discerning eye …</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>To divert myself from a troublesome fancy, 'tis but to run to my books; …</t>
+          <t>To divert myself from a troublesome fancy, 'tis but to run to my books …</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>He works best who works without any motive, neither for money, nor for fame, nor for anything else; …</t>
+          <t>He works best who works without any motive, neither for money, nor for fame, nor for anything else …</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>Let us do good because it is good to do good; …</t>
+          <t>Let us do good because it is good to do good …</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
@@ -26507,7 +26507,7 @@
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>The true prevails, not the untrue; …</t>
+          <t>The true prevails, not the untrue …</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
@@ -28697,7 +28697,7 @@
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>He who stands on his tiptoes does not stand firm; he who stretches his legs does not walk easily. So, he who displays himself does not shine; he who asserts his own views is not distinguished; …</t>
+          <t>He who stands on his tiptoes does not stand firm; he who stretches his legs does not walk easily. So, he who displays himself does not shine; he who asserts his own views is not distinguished …</t>
         </is>
       </c>
       <c r="C444" s="4" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>Therefore the sage puts his own person last, and yet it is found in the foremost place; …</t>
+          <t>Therefore the sage puts his own person last, and yet it is found in the foremost place …</t>
         </is>
       </c>
       <c r="C448" s="4" t="inlineStr">
@@ -29197,7 +29197,7 @@
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>Favour and disgrace would seem equally to be feared; …</t>
+          <t>Favour and disgrace would seem equally to be feared …</t>
         </is>
       </c>
       <c r="C452" s="4" t="inlineStr">
@@ -38460,7 +38460,7 @@
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>Saying this one is my enemy, and this one my foe, / While it is his own body which is his enemy and foe, …</t>
+          <t>Saying this one is my enemy, and this one my foe, / While it is his own body which is his enemy and foe …</t>
         </is>
       </c>
       <c r="C598" s="4" t="inlineStr">

--- a/content/thoughts.xlsx
+++ b/content/thoughts.xlsx
@@ -34101,7 +34101,7 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. I</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. I</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
@@ -34152,7 +34152,7 @@
       </c>
       <c r="N529" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura was a Japanese art expert who wrote The Book of Tea in English, published in New York in 1906, to explain the tea ceremony, and Asian ideas of beauty, to Western readers.
+          <t>Okakura Kakuzō was a Japanese art expert who wrote The Book of Tea in English, published in New York in 1906, to explain the tea ceremony, and Asian ideas of beauty, to Western readers.
 Those who cannot feel the littleness of great things in themselves, he says, tend to overlook the greatness of little things in others. It is a subtle line. If we think too much of our own importance, we miss the quiet value of small things, like a cup of tea, a simple room, or another person's modest gift. Humility opens our eyes to them.</t>
         </is>
       </c>
@@ -34168,7 +34168,7 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. I</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. I</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
@@ -34219,7 +34219,7 @@
       </c>
       <c r="N530" s="2" t="inlineStr">
         <is>
-          <t>The first chapter of Kakuzo Okakura's The Book of Tea, written in English and published in New York in 1906, ends with a picture of an afternoon: light on the bamboos, fountains bubbling, the sound of pines in the kettle. Meanwhile, he says, let us have a sip of tea.
+          <t>The first chapter of Okakura Kakuzō's The Book of Tea, written in English and published in New York in 1906, ends with a picture of an afternoon: light on the bamboos, fountains bubbling, the sound of pines in the kettle. Meanwhile, he says, let us have a sip of tea.
 Let us dream of evanescence, and linger in the beautiful foolishness of things. Evanescence means passing away, like steam or blossom. Okakura invites us to stop worrying about large problems for a moment, and enjoy what is fleeting and small. It is not a call to ignore the world. It is a reminder that beauty lives in passing moments, if we pause for them.</t>
         </is>
       </c>
@@ -34235,12 +34235,12 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. III</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. III</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura wrote The Book of Tea in English in 1906 to explain Japanese culture to the West. Drawing on Taoism, he says living well means constantly adjusting, not following a fixed recipe.</t>
+          <t>Okakura Kakuzō wrote The Book of Tea in English in 1906 to explain Japanese culture to the West. Drawing on Taoism, he says living well means constantly adjusting, not following a fixed recipe.</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="N531" s="2" t="inlineStr">
         <is>
-          <t>In the third chapter of Kakuzo Okakura's The Book of Tea, written in English and published in New York in 1906, he explains how Taoism shaped Japanese ideas of beauty. Taoism, he says, deals with the present: with ourselves.
+          <t>In the third chapter of Okakura Kakuzō's The Book of Tea, written in English and published in New York in 1906, he explains how Taoism shaped Japanese ideas of beauty. Taoism, he says, deals with the present: with ourselves.
 The art of life, he writes, lies in constant readjustment to our surroundings. Nothing stays still, so we must keep adapting, like water finding its way. Taoism, he adds, accepts the everyday world as it is, and tries to find beauty in it. It is a gentle philosophy of flexibility. Living well isn't following one fixed plan, but adjusting gracefully as things change.</t>
         </is>
       </c>
@@ -34298,7 +34298,7 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. II</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. II</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
@@ -34349,7 +34349,7 @@
       </c>
       <c r="N532" s="2" t="inlineStr">
         <is>
-          <t>In the second chapter of Kakuzo Okakura's The Book of Tea, he says that the different ways people have drunk tea over the centuries reflect the spirit of each age.
+          <t>In the second chapter of Okakura Kakuzō's The Book of Tea, he says that the different ways people have drunk tea over the centuries reflect the spirit of each age.
 Life is an expression, he says, and our unconscious actions constantly betray our innermost thoughts. Then the ironic line: perhaps we reveal ourselves too much in small things because we have so little of the great to hide. How we drink tea, set a table or greet a guest shows who we are. Small habits, Okakura suggests, say more about us than grand words.</t>
         </is>
       </c>
@@ -34365,7 +34365,7 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. III</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. III</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
@@ -34416,7 +34416,7 @@
       </c>
       <c r="N533" s="2" t="inlineStr">
         <is>
-          <t>In the third chapter of Kakuzo Okakura's The Book of Tea, he explains Laozi's favourite image: the emptiness that makes things useful.
+          <t>In the third chapter of Okakura Kakuzō's The Book of Tea, he explains Laozi's favourite image: the emptiness that makes things useful.
 The reality of a room, he says, is the empty space inside the roof and walls, not the roof and walls themselves. The usefulness of a water pitcher is in the emptiness where water can go, not in its form or material. Okakura applies the idea to the tea room, which is kept almost empty. Space, silence and simplicity aren't absence. They make room for what matters.</t>
         </is>
       </c>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. IV</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. IV</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
@@ -34495,7 +34495,7 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. III</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. III</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
@@ -34542,7 +34542,7 @@
       </c>
       <c r="N535" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura explains, in the third chapter of The Book of Tea (1906), how Taoist ideas of emptiness shaped Japanese art and even the martial art of jiu-jitsu.
+          <t>Okakura Kakuzō explains, in the third chapter of The Book of Tea (1906), how Taoist ideas of emptiness shaped Japanese art and even the martial art of jiu-jitsu.
 In art, he says, the same principle appears as the value of suggestion. By leaving something unsaid, the artist gives the viewer a chance to complete the idea, and so a great masterpiece holds our attention until we seem to become part of it. It applies to conversation and writing too. Leaving room for the listener can say more than saying everything.</t>
         </is>
       </c>
@@ -34558,7 +34558,7 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. VII</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. VII</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
@@ -34605,7 +34605,7 @@
       <c r="M536" s="2" t="inlineStr"/>
       <c r="N536" s="2" t="inlineStr">
         <is>
-          <t>The last chapter of Kakuzo Okakura's The Book of Tea, written in English and published in New York in 1906, tells the story of the great tea master Rikiu, who fell out with his patron, the warlord Hideyoshi, and was condemned to die. Just before, Okakura reflects on facing the storms of life calmly.
+          <t>The last chapter of Okakura Kakuzō's The Book of Tea, written in English and published in New York in 1906, tells the story of the great tea master Rikiu, who fell out with his patron, the warlord Hideyoshi, and was condemned to die. Just before, Okakura reflects on facing the storms of life calmly.
 Only those who have lived with the beautiful can die beautifully, he writes. The last moments of the great tea masters, he goes on, were as refined as their lives. It is a striking thought. A life spent attending to beauty, calm and grace prepares us for its end. How we live shapes how we can meet death.</t>
         </is>
       </c>
@@ -34621,7 +34621,7 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. IV</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. IV</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
@@ -34668,7 +34668,7 @@
       <c r="M537" s="2" t="inlineStr"/>
       <c r="N537" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura tells, in the fourth chapter of The Book of Tea (1906), a story about the great tea master Rikiu and his son. Rikiu watched the young man sweep and water the garden path, until not a twig or leaf was left on the ground.
+          <t>Okakura Kakuzō tells, in the fourth chapter of The Book of Tea (1906), a story about the great tea master Rikiu and his son. Rikiu watched the young man sweep and water the garden path, until not a twig or leaf was left on the ground.
 Young fool, the tea master said, that is not how a garden path should be swept. He stepped into the garden, shook a tree, and scattered golden and crimson leaves over the path. Rikiu wanted cleanliness, but also beauty and nature. A perfectly bare path is tidy but lifeless. A few fallen leaves make it real, and beautiful.</t>
         </is>
       </c>
@@ -34684,7 +34684,7 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. IV</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. IV</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
@@ -35503,7 +35503,7 @@
       </c>
       <c r="C551" s="4" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. I</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. I</t>
         </is>
       </c>
       <c r="D551" s="4" t="inlineStr">
@@ -35550,7 +35550,7 @@
       <c r="M551" s="4" t="inlineStr"/>
       <c r="N551" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura wrote The Book of Tea in English, published in New York in 1906, partly to answer Western mockery of Asia. You may laugh at us for having too much tea, he says, but perhaps you have no tea in your constitution.
+          <t>Okakura Kakuzō wrote The Book of Tea in English, published in New York in 1906, partly to answer Western mockery of Asia. You may laugh at us for having too much tea, he says, but perhaps you have no tea in your constitution.
 We have developed along different lines, he goes on, but there is no reason why one should not supplement the other. It is a generous and hopeful message, written at a time of rivalry and misunderstanding. East and West, or any two cultures, need not compete. Each has gained something the other lacks. Learning from each other makes both richer.</t>
         </is>
       </c>
@@ -35566,7 +35566,7 @@
       </c>
       <c r="C552" s="4" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. I</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. I</t>
         </is>
       </c>
       <c r="D552" s="4" t="inlineStr">
@@ -35613,7 +35613,7 @@
       <c r="M552" s="4" t="inlineStr"/>
       <c r="N552" s="2" t="inlineStr">
         <is>
-          <t>In the first chapter of Kakuzo Okakura's The Book of Tea, he asks East and West to stop trading insults and learn from each other.
+          <t>In the first chapter of Okakura Kakuzō's The Book of Tea, he asks East and West to stop trading insults and learn from each other.
 You have gained expansion at the cost of restlessness, he says to the West; we have created a harmony that is weak against aggression. Each civilisation has paid a price for its strengths. It is an honest, balanced assessment. Neither side has everything right. Seeing our own costs, and the other's gifts, is the beginning of real exchange.</t>
         </is>
       </c>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="C553" s="4" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. V</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. V</t>
         </is>
       </c>
       <c r="D553" s="4" t="inlineStr">
@@ -35676,7 +35676,7 @@
       <c r="M553" s="4" t="inlineStr"/>
       <c r="N553" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura's chapter on art appreciation in The Book of Tea (1906) describes how a great work speaks to us: memories long forgotten come back with new meaning, and hidden hopes and longings stand forth.
+          <t>Okakura Kakuzō's chapter on art appreciation in The Book of Tea (1906) describes how a great work speaks to us: memories long forgotten come back with new meaning, and hidden hopes and longings stand forth.
 Our mind is the canvas on which artists lay their colour, he says; their pigments are our emotions. The masterpiece is of ourselves, as we are of the masterpiece. Art isn't only out there, to be looked at. It lives in the meeting between the work and the viewer. What we bring changes what we see, and what we see changes us.</t>
         </is>
       </c>
@@ -35692,7 +35692,7 @@
       </c>
       <c r="C554" s="4" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. VI</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. VI</t>
         </is>
       </c>
       <c r="D554" s="4" t="inlineStr">
@@ -35739,7 +35739,7 @@
       <c r="M554" s="4" t="inlineStr"/>
       <c r="N554" s="2" t="inlineStr">
         <is>
-          <t>In the sixth chapter of Kakuzo Okakura's The Book of Tea, he writes about flowers, and how offering the first garland made humans rise above crude necessity.
+          <t>In the sixth chapter of Okakura Kakuzō's The Book of Tea, he writes about flowers, and how offering the first garland made humans rise above crude necessity.
 In joy or sadness, he says, flowers are our constant friends. We eat, drink, sing, dance and celebrate with them. We marry and name our children with them. We dare not die without them. It is a warm tribute to how deeply flowers are woven into human life, at every important moment. They mark our joys and comfort our griefs.</t>
         </is>
       </c>
@@ -35755,7 +35755,7 @@
       </c>
       <c r="C555" s="4" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura, The Book of Tea, ch. III</t>
+          <t>Okakura Kakuzō, The Book of Tea, ch. III</t>
         </is>
       </c>
       <c r="D555" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="N555" s="2" t="inlineStr">
         <is>
-          <t>Taoism, Kakuzo Okakura writes in the third chapter of The Book of Tea (1906), has always been called by Chinese historians the art of being in the world, because it deals with the present, with ourselves.
+          <t>Taoism, Okakura Kakuzō writes in the third chapter of The Book of Tea (1906), has always been called by Chinese historians the art of being in the world, because it deals with the present, with ourselves.
 The present is the moving infinity, he says, the true sphere of the relative. Everything changes, so everything must be understood in relation to the moment. The next line draws the lesson: the art of life lies in constant readjustment to our surroundings. It is a dense, poetic phrase. The present is where the endless and the changing meet, and where we actually live.</t>
         </is>
       </c>
@@ -41354,6 +41354,7 @@
         <v>2.54</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
